--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J724"/>
+  <dimension ref="A1:J725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26506,6 +26506,42 @@
       <c r="J724" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>273.79</v>
+      </c>
+      <c r="C725" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="D725" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="E725" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="F725" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="G725" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="H725" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="I725" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B735"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33873,6 +33909,16 @@
       </c>
       <c r="B735" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -34041,28 +34087,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197380104041358</v>
+        <v>0.1796121224972418</v>
       </c>
       <c r="J2" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K2" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001629196534730926</v>
+        <v>0.001348370324727566</v>
       </c>
       <c r="M2" t="n">
-        <v>30.98760190424119</v>
+        <v>31.03242639362215</v>
       </c>
       <c r="N2" t="n">
-        <v>1249.882374663546</v>
+        <v>1253.236539162413</v>
       </c>
       <c r="O2" t="n">
-        <v>35.35367554673129</v>
+        <v>35.40108104510954</v>
       </c>
       <c r="P2" t="n">
-        <v>329.388602338102</v>
+        <v>329.5743766581289</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34119,28 +34165,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.844257409956329</v>
+        <v>0.8458547422363022</v>
       </c>
       <c r="J3" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K3" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4476065020430162</v>
+        <v>0.4491256193212746</v>
       </c>
       <c r="M3" t="n">
-        <v>5.463555381045524</v>
+        <v>5.464408900444515</v>
       </c>
       <c r="N3" t="n">
-        <v>46.05172855008415</v>
+        <v>46.02918153861351</v>
       </c>
       <c r="O3" t="n">
-        <v>6.786142390937885</v>
+        <v>6.784480933617067</v>
       </c>
       <c r="P3" t="n">
-        <v>336.9912654703071</v>
+        <v>336.974564455764</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34197,28 +34243,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9962858358494548</v>
+        <v>0.9971703877018884</v>
       </c>
       <c r="J4" t="n">
+        <v>724</v>
+      </c>
+      <c r="K4" t="n">
         <v>723</v>
       </c>
-      <c r="K4" t="n">
-        <v>722</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6067615253924674</v>
+        <v>0.6078735695041446</v>
       </c>
       <c r="M4" t="n">
-        <v>4.551252569285595</v>
+        <v>4.549752433416643</v>
       </c>
       <c r="N4" t="n">
-        <v>33.51971393772004</v>
+        <v>33.4858552570979</v>
       </c>
       <c r="O4" t="n">
-        <v>5.789621225755623</v>
+        <v>5.786696402706634</v>
       </c>
       <c r="P4" t="n">
-        <v>341.0579636437303</v>
+        <v>341.0486848076361</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34275,28 +34321,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.090570753987775</v>
+        <v>1.089869944281553</v>
       </c>
       <c r="J5" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K5" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6737926124450083</v>
+        <v>0.6741674421865529</v>
       </c>
       <c r="M5" t="n">
-        <v>4.411868669396943</v>
+        <v>4.408743072908362</v>
       </c>
       <c r="N5" t="n">
-        <v>30.14527455076268</v>
+        <v>30.11154116511383</v>
       </c>
       <c r="O5" t="n">
-        <v>5.490471250335682</v>
+        <v>5.487398396791856</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0767990902847</v>
+        <v>353.0841264530647</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34353,28 +34399,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8572797581029936</v>
+        <v>0.8566526606950661</v>
       </c>
       <c r="J6" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K6" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5823218009897055</v>
+        <v>0.5827013913317562</v>
       </c>
       <c r="M6" t="n">
-        <v>4.154907447360589</v>
+        <v>4.152130493438357</v>
       </c>
       <c r="N6" t="n">
-        <v>27.59738290185116</v>
+        <v>27.56559348890777</v>
       </c>
       <c r="O6" t="n">
-        <v>5.25332113066117</v>
+        <v>5.250294609725036</v>
       </c>
       <c r="P6" t="n">
-        <v>354.1264101859518</v>
+        <v>354.1329668448644</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34431,28 +34477,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4142294695771447</v>
+        <v>0.414956772483149</v>
       </c>
       <c r="J7" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K7" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2588250214336129</v>
+        <v>0.2600606599026156</v>
       </c>
       <c r="M7" t="n">
-        <v>3.900740160020619</v>
+        <v>3.89852919954777</v>
       </c>
       <c r="N7" t="n">
-        <v>25.72411715159545</v>
+        <v>25.69709921308966</v>
       </c>
       <c r="O7" t="n">
-        <v>5.071894828522714</v>
+        <v>5.069230633250934</v>
       </c>
       <c r="P7" t="n">
-        <v>364.0116159260597</v>
+        <v>364.0040115618566</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34509,28 +34555,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3125230886177675</v>
+        <v>0.313508721179386</v>
       </c>
       <c r="J8" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K8" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1847982782420928</v>
+        <v>0.1861364229702062</v>
       </c>
       <c r="M8" t="n">
-        <v>3.671889489613208</v>
+        <v>3.671357345000533</v>
       </c>
       <c r="N8" t="n">
-        <v>22.55669075703539</v>
+        <v>22.54116882138879</v>
       </c>
       <c r="O8" t="n">
-        <v>4.749388461374306</v>
+        <v>4.747754081814769</v>
       </c>
       <c r="P8" t="n">
-        <v>356.2122370320184</v>
+        <v>356.2019316848141</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34587,28 +34633,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5325114536808688</v>
+        <v>0.5328920778798881</v>
       </c>
       <c r="J9" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K9" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4305484379708286</v>
+        <v>0.4316678111355552</v>
       </c>
       <c r="M9" t="n">
-        <v>3.473390769426</v>
+        <v>3.470301577314294</v>
       </c>
       <c r="N9" t="n">
-        <v>19.63526106178967</v>
+        <v>19.61047197890989</v>
       </c>
       <c r="O9" t="n">
-        <v>4.431169265757027</v>
+        <v>4.428371255767733</v>
       </c>
       <c r="P9" t="n">
-        <v>347.9976467709771</v>
+        <v>347.9936671291937</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34646,7 +34692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J724"/>
+  <dimension ref="A1:J725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72293,6 +72339,58 @@
         </is>
       </c>
     </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>-39.840523809940635,176.9976206582651</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>-39.841576079291876,176.99768284891897</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>-39.84207116805094,176.99706086779284</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>-39.842570022879514,176.99651874736034</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>-39.843125864656294,176.99606572681688</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>-39.843725552475334,176.9956808557529</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>-39.84433709390045,176.9953206724516</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>-39.844993628666245,176.99504684479675</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J725"/>
+  <dimension ref="A1:J728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26542,6 +26542,114 @@
       <c r="J725" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="C726" t="n">
+        <v>365.84</v>
+      </c>
+      <c r="D726" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="E726" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="F726" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="G726" t="n">
+        <v>375.34</v>
+      </c>
+      <c r="H726" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="I726" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="C727" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="D727" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="E727" t="n">
+        <v>381.07</v>
+      </c>
+      <c r="F727" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="G727" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="H727" t="n">
+        <v>365.63</v>
+      </c>
+      <c r="I727" t="n">
+        <v>363.45</v>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="C728" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="D728" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="E728" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="F728" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="G728" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="H728" t="n">
+        <v>367</v>
+      </c>
+      <c r="I728" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26556,7 +26664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33919,6 +34027,36 @@
       </c>
       <c r="B736" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -34087,28 +34225,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1796121224972418</v>
+        <v>0.1634102747657786</v>
       </c>
       <c r="J2" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K2" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001348370324727566</v>
+        <v>0.001124917886128896</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03242639362215</v>
+        <v>30.98348080270044</v>
       </c>
       <c r="N2" t="n">
-        <v>1253.236539162413</v>
+        <v>1250.705413258369</v>
       </c>
       <c r="O2" t="n">
-        <v>35.40108104510954</v>
+        <v>35.36531370224742</v>
       </c>
       <c r="P2" t="n">
-        <v>329.5743766581289</v>
+        <v>329.7441465383794</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34165,28 +34303,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8458547422363022</v>
+        <v>0.8524473225902593</v>
       </c>
       <c r="J3" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K3" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4491256193212746</v>
+        <v>0.454123769170796</v>
       </c>
       <c r="M3" t="n">
-        <v>5.464408900444515</v>
+        <v>5.476187191116321</v>
       </c>
       <c r="N3" t="n">
-        <v>46.02918153861351</v>
+        <v>46.07453960437224</v>
       </c>
       <c r="O3" t="n">
-        <v>6.784480933617067</v>
+        <v>6.787822891352738</v>
       </c>
       <c r="P3" t="n">
-        <v>336.974564455764</v>
+        <v>336.9054238064239</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34243,28 +34381,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9971703877018884</v>
+        <v>1.001096900295561</v>
       </c>
       <c r="J4" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K4" t="n">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6078735695041446</v>
+        <v>0.6114877483949033</v>
       </c>
       <c r="M4" t="n">
-        <v>4.549752433416643</v>
+        <v>4.552137106764334</v>
       </c>
       <c r="N4" t="n">
-        <v>33.4858552570979</v>
+        <v>33.42992295323469</v>
       </c>
       <c r="O4" t="n">
-        <v>5.786696402706634</v>
+        <v>5.781861547394117</v>
       </c>
       <c r="P4" t="n">
-        <v>341.0486848076361</v>
+        <v>341.0073746373797</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34321,28 +34459,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.089869944281553</v>
+        <v>1.088794723014735</v>
       </c>
       <c r="J5" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K5" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6741674421865529</v>
+        <v>0.6758293694894371</v>
       </c>
       <c r="M5" t="n">
-        <v>4.408743072908362</v>
+        <v>4.395053814385915</v>
       </c>
       <c r="N5" t="n">
-        <v>30.11154116511383</v>
+        <v>29.99401271228601</v>
       </c>
       <c r="O5" t="n">
-        <v>5.487398396791856</v>
+        <v>5.476678985688865</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0841264530647</v>
+        <v>353.0954002790537</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34399,28 +34537,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8566526606950661</v>
+        <v>0.8526238396080734</v>
       </c>
       <c r="J6" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K6" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5827013913317562</v>
+        <v>0.5820078995193532</v>
       </c>
       <c r="M6" t="n">
-        <v>4.152130493438357</v>
+        <v>4.154003992276854</v>
       </c>
       <c r="N6" t="n">
-        <v>27.56559348890777</v>
+        <v>27.53975609815159</v>
       </c>
       <c r="O6" t="n">
-        <v>5.250294609725036</v>
+        <v>5.247833467074921</v>
       </c>
       <c r="P6" t="n">
-        <v>354.1329668448644</v>
+        <v>354.1752196347829</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34477,28 +34615,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.414956772483149</v>
+        <v>0.4149141369055609</v>
       </c>
       <c r="J7" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K7" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2600606599026156</v>
+        <v>0.2619025999220268</v>
       </c>
       <c r="M7" t="n">
-        <v>3.89852919954777</v>
+        <v>3.883794943999482</v>
       </c>
       <c r="N7" t="n">
-        <v>25.69709921308966</v>
+        <v>25.59153183294623</v>
       </c>
       <c r="O7" t="n">
-        <v>5.069230633250934</v>
+        <v>5.058807352820053</v>
       </c>
       <c r="P7" t="n">
-        <v>364.0040115618566</v>
+        <v>364.0044612876141</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34555,28 +34693,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.313508721179386</v>
+        <v>0.3146024210728531</v>
       </c>
       <c r="J8" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K8" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1861364229702062</v>
+        <v>0.188613628898662</v>
       </c>
       <c r="M8" t="n">
-        <v>3.671357345000533</v>
+        <v>3.661206271390383</v>
       </c>
       <c r="N8" t="n">
-        <v>22.54116882138879</v>
+        <v>22.45870498838381</v>
       </c>
       <c r="O8" t="n">
-        <v>4.747754081814769</v>
+        <v>4.739061614748621</v>
       </c>
       <c r="P8" t="n">
-        <v>356.2019316848141</v>
+        <v>356.1904554309972</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34633,28 +34771,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5328920778798881</v>
+        <v>0.5341558478245201</v>
       </c>
       <c r="J9" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="K9" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4316678111355552</v>
+        <v>0.4350490816482008</v>
       </c>
       <c r="M9" t="n">
-        <v>3.470301577314294</v>
+        <v>3.461631638391537</v>
       </c>
       <c r="N9" t="n">
-        <v>19.61047197890989</v>
+        <v>19.54404208433631</v>
       </c>
       <c r="O9" t="n">
-        <v>4.428371255767733</v>
+        <v>4.420864404653948</v>
       </c>
       <c r="P9" t="n">
-        <v>347.9936671291937</v>
+        <v>347.9804058526653</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34692,7 +34830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J725"/>
+  <dimension ref="A1:J728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72391,6 +72529,162 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>-39.84063855181765,176.99776238836554</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>-39.84158389813323,176.99769250702172</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>-39.8420822126851,176.99707492907694</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>-39.84257446651339,176.9965268215363</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>-39.843118295906585,176.99604597311716</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>-39.84371900740616,176.99565848591718</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>-39.84433003526413,176.99528362034894</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>-39.844991145572514,176.99503249528215</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>-39.84086223600691,176.99803868696728</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>-39.841594388410606,176.99770546497973</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>-39.8420822126851,176.99707492907694</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>-39.84257906698074,176.99653518068428</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>-39.843115893128136,176.99603970210222</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>-39.843717123702476,176.99565204777005</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>-39.84433240973033,176.99529608435827</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>-39.84499394397959,176.9950486669574</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>-39.84088914582206,176.9980719266235</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>-39.84159295495665,176.99770369432684</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>-39.842079323100776,176.99707125025216</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>-39.84257582574245,176.99652929128445</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>-39.84311425122933,176.99603541690894</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>-39.843716580940324,176.99565019271077</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>-39.844335367018076,176.9953116077164</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>-39.844996978869126,176.99506620525432</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J728"/>
+  <dimension ref="A1:J729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26648,6 +26648,42 @@
         <v>364.99</v>
       </c>
       <c r="J728" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="C729" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="D729" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="E729" t="n">
+        <v>380.49</v>
+      </c>
+      <c r="F729" t="n">
+        <v>372</v>
+      </c>
+      <c r="G729" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="H729" t="n">
+        <v>368.02</v>
+      </c>
+      <c r="I729" t="n">
+        <v>365.69</v>
+      </c>
+      <c r="J729" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26664,7 +26700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34057,6 +34093,16 @@
       </c>
       <c r="B739" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -34225,28 +34271,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1634102747657786</v>
+        <v>0.1680583428872013</v>
       </c>
       <c r="J2" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K2" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001124917886128896</v>
+        <v>0.001193298817611321</v>
       </c>
       <c r="M2" t="n">
-        <v>30.98348080270044</v>
+        <v>30.96219393086489</v>
       </c>
       <c r="N2" t="n">
-        <v>1250.705413258369</v>
+        <v>1249.336513757909</v>
       </c>
       <c r="O2" t="n">
-        <v>35.36531370224742</v>
+        <v>35.34595470146348</v>
       </c>
       <c r="P2" t="n">
-        <v>329.7441465383794</v>
+        <v>329.6952469306408</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34303,28 +34349,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8524473225902593</v>
+        <v>0.8548453153544781</v>
       </c>
       <c r="J3" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K3" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L3" t="n">
-        <v>0.454123769170796</v>
+        <v>0.4558263472934454</v>
       </c>
       <c r="M3" t="n">
-        <v>5.476187191116321</v>
+        <v>5.481119174644788</v>
       </c>
       <c r="N3" t="n">
-        <v>46.07453960437224</v>
+        <v>46.10416921460008</v>
       </c>
       <c r="O3" t="n">
-        <v>6.787822891352738</v>
+        <v>6.790005096802217</v>
       </c>
       <c r="P3" t="n">
-        <v>336.9054238064239</v>
+        <v>336.8801959262665</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34381,28 +34427,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.001096900295561</v>
+        <v>1.002276390187742</v>
       </c>
       <c r="J4" t="n">
+        <v>728</v>
+      </c>
+      <c r="K4" t="n">
         <v>727</v>
       </c>
-      <c r="K4" t="n">
-        <v>726</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6114877483949033</v>
+        <v>0.6126652898737495</v>
       </c>
       <c r="M4" t="n">
-        <v>4.552137106764334</v>
+        <v>4.552194193730895</v>
       </c>
       <c r="N4" t="n">
-        <v>33.42992295323469</v>
+        <v>33.40626240717743</v>
       </c>
       <c r="O4" t="n">
-        <v>5.781861547394117</v>
+        <v>5.779815084168129</v>
       </c>
       <c r="P4" t="n">
-        <v>341.0073746373797</v>
+        <v>340.9949255223735</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34459,28 +34505,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.088794723014735</v>
+        <v>1.088390074305915</v>
       </c>
       <c r="J5" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K5" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6758293694894371</v>
+        <v>0.6763622682464925</v>
       </c>
       <c r="M5" t="n">
-        <v>4.395053814385915</v>
+        <v>4.390695095290955</v>
       </c>
       <c r="N5" t="n">
-        <v>29.99401271228601</v>
+        <v>29.95545798937351</v>
       </c>
       <c r="O5" t="n">
-        <v>5.476678985688865</v>
+        <v>5.473157953994522</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0954002790537</v>
+        <v>353.0996573515872</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34537,28 +34583,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8526238396080734</v>
+        <v>0.8512519739623495</v>
       </c>
       <c r="J6" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K6" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5820078995193532</v>
+        <v>0.5817498736860967</v>
       </c>
       <c r="M6" t="n">
-        <v>4.154003992276854</v>
+        <v>4.154807908403794</v>
       </c>
       <c r="N6" t="n">
-        <v>27.53975609815159</v>
+        <v>27.53233778922029</v>
       </c>
       <c r="O6" t="n">
-        <v>5.247833467074921</v>
+        <v>5.247126622182877</v>
       </c>
       <c r="P6" t="n">
-        <v>354.1752196347829</v>
+        <v>354.1896522313356</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34615,28 +34661,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4149141369055609</v>
+        <v>0.4150314145765203</v>
       </c>
       <c r="J7" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K7" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2619025999220268</v>
+        <v>0.262642050089069</v>
       </c>
       <c r="M7" t="n">
-        <v>3.883794943999482</v>
+        <v>3.878972740381598</v>
       </c>
       <c r="N7" t="n">
-        <v>25.59153183294623</v>
+        <v>25.55660087824762</v>
       </c>
       <c r="O7" t="n">
-        <v>5.058807352820053</v>
+        <v>5.055353684782858</v>
       </c>
       <c r="P7" t="n">
-        <v>364.0044612876141</v>
+        <v>364.003227477791</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34693,28 +34739,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3146024210728531</v>
+        <v>0.3156244083846784</v>
       </c>
       <c r="J8" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K8" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L8" t="n">
-        <v>0.188613628898662</v>
+        <v>0.1899947531552737</v>
       </c>
       <c r="M8" t="n">
-        <v>3.661206271390383</v>
+        <v>3.660839341925542</v>
       </c>
       <c r="N8" t="n">
-        <v>22.45870498838381</v>
+        <v>22.44473226167261</v>
       </c>
       <c r="O8" t="n">
-        <v>4.739061614748621</v>
+        <v>4.737587177210844</v>
       </c>
       <c r="P8" t="n">
-        <v>356.1904554309972</v>
+        <v>356.1797036998787</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34771,28 +34817,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5341558478245201</v>
+        <v>0.5351995257017709</v>
       </c>
       <c r="J9" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K9" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4350490816482008</v>
+        <v>0.4365901959277132</v>
       </c>
       <c r="M9" t="n">
-        <v>3.461631638391537</v>
+        <v>3.461582056718978</v>
       </c>
       <c r="N9" t="n">
-        <v>19.54404208433631</v>
+        <v>19.53479701571768</v>
       </c>
       <c r="O9" t="n">
-        <v>4.420864404653948</v>
+        <v>4.419818663216589</v>
       </c>
       <c r="P9" t="n">
-        <v>347.9804058526653</v>
+        <v>347.969425927787</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34830,7 +34876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J728"/>
+  <dimension ref="A1:J729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72685,6 +72731,58 @@
         </is>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>-39.84102063236443,176.9982343425589</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>-39.841595887021526,176.9977073161169</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>-39.842079258887786,176.9970711685005</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>-39.8425760348546,176.9965296712457</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>-39.84311581303552,176.99603949306842</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>-39.84371913511487,176.99565892240173</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-39.84433756879299,176.99532316525386</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>-39.84499835836347,176.99507417720793</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J729"/>
+  <dimension ref="A1:J732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26684,6 +26684,114 @@
         <v>365.69</v>
       </c>
       <c r="J729" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:40+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="C730" t="n">
+        <v>369.03</v>
+      </c>
+      <c r="D730" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="E730" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="F730" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="G730" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="H730" t="n">
+        <v>369.57</v>
+      </c>
+      <c r="I730" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="C731" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="D731" t="n">
+        <v>373.31</v>
+      </c>
+      <c r="E731" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="F731" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="G731" t="n">
+        <v>377.82</v>
+      </c>
+      <c r="H731" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="I731" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="C732" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="D732" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="E732" t="n">
+        <v>383.53</v>
+      </c>
+      <c r="F732" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="G732" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="H732" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="I732" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="J732" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26700,7 +26808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34103,6 +34211,36 @@
       </c>
       <c r="B740" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -34271,28 +34409,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1680583428872013</v>
+        <v>0.2017169324849823</v>
       </c>
       <c r="J2" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K2" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001193298817611321</v>
+        <v>0.001726977126555118</v>
       </c>
       <c r="M2" t="n">
-        <v>30.96219393086489</v>
+        <v>30.9870851139123</v>
       </c>
       <c r="N2" t="n">
-        <v>1249.336513757909</v>
+        <v>1250.250806501055</v>
       </c>
       <c r="O2" t="n">
-        <v>35.34595470146348</v>
+        <v>35.35888582097936</v>
       </c>
       <c r="P2" t="n">
-        <v>329.6952469306408</v>
+        <v>329.339179035939</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34349,28 +34487,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8548453153544781</v>
+        <v>0.8636864881650204</v>
       </c>
       <c r="J3" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K3" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4558263472934454</v>
+        <v>0.4611504144441204</v>
       </c>
       <c r="M3" t="n">
-        <v>5.481119174644788</v>
+        <v>5.504261116829444</v>
       </c>
       <c r="N3" t="n">
-        <v>46.10416921460008</v>
+        <v>46.33262265274574</v>
       </c>
       <c r="O3" t="n">
-        <v>6.790005096802217</v>
+        <v>6.806807082086706</v>
       </c>
       <c r="P3" t="n">
-        <v>336.8801959262665</v>
+        <v>336.7866641979018</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34427,28 +34565,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.002276390187742</v>
+        <v>1.006886143787965</v>
       </c>
       <c r="J4" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K4" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6126652898737495</v>
+        <v>0.6163919805036016</v>
       </c>
       <c r="M4" t="n">
-        <v>4.552194193730895</v>
+        <v>4.558001871047147</v>
       </c>
       <c r="N4" t="n">
-        <v>33.40626240717743</v>
+        <v>33.38193257875203</v>
       </c>
       <c r="O4" t="n">
-        <v>5.779815084168129</v>
+        <v>5.777709977036926</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9949255223735</v>
+        <v>340.9460049524893</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34505,28 +34643,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.088390074305915</v>
+        <v>1.089391282627428</v>
       </c>
       <c r="J5" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K5" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6763622682464925</v>
+        <v>0.6788876969720937</v>
       </c>
       <c r="M5" t="n">
-        <v>4.390695095290955</v>
+        <v>4.377895104694594</v>
       </c>
       <c r="N5" t="n">
-        <v>29.95545798937351</v>
+        <v>29.83846528821372</v>
       </c>
       <c r="O5" t="n">
-        <v>5.473157953994522</v>
+        <v>5.462459637215979</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0996573515872</v>
+        <v>353.0890627559027</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34583,28 +34721,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8512519739623495</v>
+        <v>0.8498285709484864</v>
       </c>
       <c r="J6" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K6" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5817498736860967</v>
+        <v>0.5832233335796451</v>
       </c>
       <c r="M6" t="n">
-        <v>4.154807908403794</v>
+        <v>4.144403365809596</v>
       </c>
       <c r="N6" t="n">
-        <v>27.53233778922029</v>
+        <v>27.43347636738688</v>
       </c>
       <c r="O6" t="n">
-        <v>5.247126622182877</v>
+        <v>5.237697620843234</v>
       </c>
       <c r="P6" t="n">
-        <v>354.1896522313356</v>
+        <v>354.2047015683819</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34661,28 +34799,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4150314145765203</v>
+        <v>0.4171971049827137</v>
       </c>
       <c r="J7" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K7" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L7" t="n">
-        <v>0.262642050089069</v>
+        <v>0.2663957355034589</v>
       </c>
       <c r="M7" t="n">
-        <v>3.878972740381598</v>
+        <v>3.872421263030377</v>
       </c>
       <c r="N7" t="n">
-        <v>25.55660087824762</v>
+        <v>25.47808807495275</v>
       </c>
       <c r="O7" t="n">
-        <v>5.055353684782858</v>
+        <v>5.047582399025572</v>
       </c>
       <c r="P7" t="n">
-        <v>364.003227477791</v>
+        <v>363.9803125388084</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34739,28 +34877,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3156244083846784</v>
+        <v>0.32198079687694</v>
       </c>
       <c r="J8" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K8" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1899947531552737</v>
+        <v>0.1961792143559478</v>
       </c>
       <c r="M8" t="n">
-        <v>3.660839341925542</v>
+        <v>3.674636229976075</v>
       </c>
       <c r="N8" t="n">
-        <v>22.44473226167261</v>
+        <v>22.57958036752528</v>
       </c>
       <c r="O8" t="n">
-        <v>4.737587177210844</v>
+        <v>4.751797593282492</v>
       </c>
       <c r="P8" t="n">
-        <v>356.1797036998787</v>
+        <v>356.1124462684</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34817,28 +34955,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5351995257017709</v>
+        <v>0.5412997591884672</v>
       </c>
       <c r="J9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4365901959277132</v>
+        <v>0.4419343440260336</v>
       </c>
       <c r="M9" t="n">
-        <v>3.461582056718978</v>
+        <v>3.474730726789613</v>
       </c>
       <c r="N9" t="n">
-        <v>19.53479701571768</v>
+        <v>19.66766916762436</v>
       </c>
       <c r="O9" t="n">
-        <v>4.419818663216589</v>
+        <v>4.434824592655763</v>
       </c>
       <c r="P9" t="n">
-        <v>347.969425927787</v>
+        <v>347.9048757769683</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34876,7 +35014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J729"/>
+  <dimension ref="A1:J732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72783,6 +72921,162 @@
         </is>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:40+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-39.84116286949466,176.99841003899257</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-39.84160468321536,176.99771818148895</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-39.842087735001456,176.99708195972067</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-39.84258706551902,176.9965497142055</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-39.84312358201786,176.99605976935143</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-39.843723317574174,176.99567321727199</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-39.8443409146251,176.9953407281797</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-39.845000348775734,176.99508567959862</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-39.84116945031647,176.99841816788782</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-39.8416106776579,176.99772558604036</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>-39.84209081722431,176.9970858838014</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-39.84259119548245,176.9965572184433</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-39.843129588960394,176.9960754468929</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-39.843726925342935,176.99568554796286</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-39.84434689394405,176.99537211483155</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-39.84500582733016,176.99511733964724</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-39.84117433706493,176.9984242041972</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-39.8416126323673,176.99772800056832</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-39.842085937038036,176.99707967067374</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-39.84259192737465,176.9965585483083</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-39.84313239219944,176.99608276307978</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-39.84372762774022,176.9956879486285</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-39.84434974329149,176.99538707164928</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-39.84500957166078,176.99513897781247</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J732"/>
+  <dimension ref="A1:J735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26792,6 +26792,114 @@
         <v>371.38</v>
       </c>
       <c r="J732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="C733" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="D733" t="n">
+        <v>371.86</v>
+      </c>
+      <c r="E733" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="F733" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="G733" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="H733" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="I733" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="C734" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="D734" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="E734" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="F734" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="G734" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="H734" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="I734" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>371.59</v>
+      </c>
+      <c r="C735" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="D735" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="E735" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="F735" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="G735" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="H735" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="I735" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="J735" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26808,7 +26916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34241,6 +34349,36 @@
       </c>
       <c r="B743" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -34409,28 +34547,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2017169324849823</v>
+        <v>0.234483212097899</v>
       </c>
       <c r="J2" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K2" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001726977126555118</v>
+        <v>0.00234468443611846</v>
       </c>
       <c r="M2" t="n">
-        <v>30.9870851139123</v>
+        <v>31.00700448926968</v>
       </c>
       <c r="N2" t="n">
-        <v>1250.250806501055</v>
+        <v>1250.87916206913</v>
       </c>
       <c r="O2" t="n">
-        <v>35.35888582097936</v>
+        <v>35.36777010314801</v>
       </c>
       <c r="P2" t="n">
-        <v>329.339179035939</v>
+        <v>328.9908830401504</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34487,28 +34625,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8636864881650204</v>
+        <v>0.872010664692248</v>
       </c>
       <c r="J3" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K3" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4611504144441204</v>
+        <v>0.4664012643417158</v>
       </c>
       <c r="M3" t="n">
-        <v>5.504261116829444</v>
+        <v>5.525344679728077</v>
       </c>
       <c r="N3" t="n">
-        <v>46.33262265274574</v>
+        <v>46.51514657125457</v>
       </c>
       <c r="O3" t="n">
-        <v>6.806807082086706</v>
+        <v>6.820201358556401</v>
       </c>
       <c r="P3" t="n">
-        <v>336.7866641979018</v>
+        <v>336.6981836727671</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34565,28 +34703,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.006886143787965</v>
+        <v>1.009413705222003</v>
       </c>
       <c r="J4" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K4" t="n">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6163919805036016</v>
+        <v>0.6196716852962683</v>
       </c>
       <c r="M4" t="n">
-        <v>4.558001871047147</v>
+        <v>4.552734179778994</v>
       </c>
       <c r="N4" t="n">
-        <v>33.38193257875203</v>
+        <v>33.28198633275115</v>
       </c>
       <c r="O4" t="n">
-        <v>5.777709977036926</v>
+        <v>5.769054197418424</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9460049524893</v>
+        <v>340.9190560491504</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34643,28 +34781,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.089391282627428</v>
+        <v>1.08764608995421</v>
       </c>
       <c r="J5" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K5" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6788876969720937</v>
+        <v>0.680173940539198</v>
       </c>
       <c r="M5" t="n">
-        <v>4.377895104694594</v>
+        <v>4.367500813132856</v>
       </c>
       <c r="N5" t="n">
-        <v>29.83846528821372</v>
+        <v>29.7416317751557</v>
       </c>
       <c r="O5" t="n">
-        <v>5.462459637215979</v>
+        <v>5.453588889452129</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0890627559027</v>
+        <v>353.1076223926465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34721,28 +34859,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8498285709484864</v>
+        <v>0.8477473354586412</v>
       </c>
       <c r="J6" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K6" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5832233335796451</v>
+        <v>0.5842175536030056</v>
       </c>
       <c r="M6" t="n">
-        <v>4.144403365809596</v>
+        <v>4.137010422449372</v>
       </c>
       <c r="N6" t="n">
-        <v>27.43347636738688</v>
+        <v>27.34765821134811</v>
       </c>
       <c r="O6" t="n">
-        <v>5.237697620843234</v>
+        <v>5.229498848967089</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2047015683819</v>
+        <v>354.2268299291347</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34799,28 +34937,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4171971049827137</v>
+        <v>0.4189796822160561</v>
       </c>
       <c r="J7" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K7" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2663957355034589</v>
+        <v>0.2698762037141665</v>
       </c>
       <c r="M7" t="n">
-        <v>3.872421263030377</v>
+        <v>3.86431494807354</v>
       </c>
       <c r="N7" t="n">
-        <v>25.47808807495275</v>
+        <v>25.39297383015816</v>
       </c>
       <c r="O7" t="n">
-        <v>5.047582399025572</v>
+        <v>5.039144156516874</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9803125388084</v>
+        <v>363.9613682305665</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34877,28 +35015,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.32198079687694</v>
+        <v>0.3289403062594484</v>
       </c>
       <c r="J8" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K8" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1961792143559478</v>
+        <v>0.2027642099476504</v>
       </c>
       <c r="M8" t="n">
-        <v>3.674636229976075</v>
+        <v>3.691114364609127</v>
       </c>
       <c r="N8" t="n">
-        <v>22.57958036752528</v>
+        <v>22.74706666309479</v>
       </c>
       <c r="O8" t="n">
-        <v>4.751797593282492</v>
+        <v>4.769388499912204</v>
       </c>
       <c r="P8" t="n">
-        <v>356.1124462684</v>
+        <v>356.0384706665126</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34955,28 +35093,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5412997591884672</v>
+        <v>0.5482865613317549</v>
       </c>
       <c r="J9" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K9" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4419343440260336</v>
+        <v>0.4474467010024042</v>
       </c>
       <c r="M9" t="n">
-        <v>3.474730726789613</v>
+        <v>3.491940018691825</v>
       </c>
       <c r="N9" t="n">
-        <v>19.66766916762436</v>
+        <v>19.84923605815076</v>
       </c>
       <c r="O9" t="n">
-        <v>4.434824592655763</v>
+        <v>4.455248147763575</v>
       </c>
       <c r="P9" t="n">
-        <v>347.9048757769683</v>
+        <v>347.830610581047</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35014,7 +35152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J732"/>
+  <dimension ref="A1:J735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73077,6 +73215,162 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-39.84117205658235,176.99842138725273</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-39.84161158985563,176.99772671282005</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-39.842081506342275,176.9970740298086</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-39.84258513123216,176.99654619956283</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-39.84313075030234,176.9960784778845</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-39.84372801086601,176.9956892580825</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-39.84434918205655,176.99538412560935</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-39.84500896074397,176.99513544737485</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-39.84116690920716,176.9984150290073</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-39.84160826684955,176.9977226081228</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-39.84207097541196,176.9970606225379</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-39.842568768206306,176.99651646759315</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-39.843123301693815,176.99605903773292</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-39.84372341335566,176.99567354463542</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-39.84434710980377,176.99537324792377</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-39.84500744330494,176.99512667822356</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-39.8411610451083,176.99840778543773</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-39.84160201177884,176.99771488163492</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-39.842070204856,176.99705964151826</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-39.842569134152654,176.99651713252524</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-39.843123381786405,176.9960592467668</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-39.8437231260112,176.99567256254505</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-39.844346872358074,176.99537200152233</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-39.8450065367826,176.99512143950997</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J735"/>
+  <dimension ref="A1:J739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26902,6 +26902,150 @@
       <c r="J735" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="C736" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="D736" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="E736" t="n">
+        <v>379.73</v>
+      </c>
+      <c r="F736" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="G736" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="H736" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="I736" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="C737" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="D737" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="E737" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="F737" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="G737" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="H737" t="n">
+        <v>372.26</v>
+      </c>
+      <c r="I737" t="n">
+        <v>370.28</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="C738" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="D738" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="E738" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="F738" t="n">
+        <v>373.53</v>
+      </c>
+      <c r="G738" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="H738" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="I738" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="C739" t="n">
+        <v>363.92</v>
+      </c>
+      <c r="D739" t="n">
+        <v>368.27</v>
+      </c>
+      <c r="E739" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="F739" t="n">
+        <v>373.19</v>
+      </c>
+      <c r="G739" t="n">
+        <v>376.12</v>
+      </c>
+      <c r="H739" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="I739" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26916,7 +27060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34379,6 +34523,46 @@
       </c>
       <c r="B746" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -34547,28 +34731,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.234483212097899</v>
+        <v>0.2717462045574097</v>
       </c>
       <c r="J2" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K2" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00234468443611846</v>
+        <v>0.003173665167479078</v>
       </c>
       <c r="M2" t="n">
-        <v>31.00700448926968</v>
+        <v>31.00538869066966</v>
       </c>
       <c r="N2" t="n">
-        <v>1250.87916206913</v>
+        <v>1249.777542851336</v>
       </c>
       <c r="O2" t="n">
-        <v>35.36777010314801</v>
+        <v>35.35219290017715</v>
       </c>
       <c r="P2" t="n">
-        <v>328.9908830401504</v>
+        <v>328.5937846889111</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34625,28 +34809,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.872010664692248</v>
+        <v>0.8786940379325925</v>
       </c>
       <c r="J3" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K3" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4664012643417158</v>
+        <v>0.4724360379790395</v>
       </c>
       <c r="M3" t="n">
-        <v>5.525344679728077</v>
+        <v>5.530869032661677</v>
       </c>
       <c r="N3" t="n">
-        <v>46.51514657125457</v>
+        <v>46.45738992645208</v>
       </c>
       <c r="O3" t="n">
-        <v>6.820201358556401</v>
+        <v>6.815965810246709</v>
       </c>
       <c r="P3" t="n">
-        <v>336.6981836727671</v>
+        <v>336.626970145074</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34703,28 +34887,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.009413705222003</v>
+        <v>1.010975196373253</v>
       </c>
       <c r="J4" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6196716852962683</v>
+        <v>0.6234119832283921</v>
       </c>
       <c r="M4" t="n">
-        <v>4.552734179778994</v>
+        <v>4.536209618015935</v>
       </c>
       <c r="N4" t="n">
-        <v>33.28198633275115</v>
+        <v>33.11371645875008</v>
       </c>
       <c r="O4" t="n">
-        <v>5.769054197418424</v>
+        <v>5.754451881695604</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9190560491504</v>
+        <v>340.9023669366072</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34781,28 +34965,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.08764608995421</v>
+        <v>1.083972436473473</v>
       </c>
       <c r="J5" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K5" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.680173940539198</v>
+        <v>0.6811467364951451</v>
       </c>
       <c r="M5" t="n">
-        <v>4.367500813132856</v>
+        <v>4.359044099152356</v>
       </c>
       <c r="N5" t="n">
-        <v>29.7416317751557</v>
+        <v>29.63698422676292</v>
       </c>
       <c r="O5" t="n">
-        <v>5.453588889452129</v>
+        <v>5.443986060485728</v>
       </c>
       <c r="P5" t="n">
-        <v>353.1076223926465</v>
+        <v>353.1467768841694</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34859,28 +35043,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8477473354586412</v>
+        <v>0.8438471017360613</v>
       </c>
       <c r="J6" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K6" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5842175536030056</v>
+        <v>0.5846152933036199</v>
       </c>
       <c r="M6" t="n">
-        <v>4.137010422449372</v>
+        <v>4.132338643486166</v>
       </c>
       <c r="N6" t="n">
-        <v>27.34765821134811</v>
+        <v>27.26184233936884</v>
       </c>
       <c r="O6" t="n">
-        <v>5.229498848967089</v>
+        <v>5.221287421639307</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2268299291347</v>
+        <v>354.2683973594289</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34937,28 +35121,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4189796822160561</v>
+        <v>0.419917969661494</v>
       </c>
       <c r="J7" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K7" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2698762037141665</v>
+        <v>0.2733247887720994</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86431494807354</v>
+        <v>3.847398849827586</v>
       </c>
       <c r="N7" t="n">
-        <v>25.39297383015816</v>
+        <v>25.2602467760445</v>
       </c>
       <c r="O7" t="n">
-        <v>5.039144156516874</v>
+        <v>5.025957299464898</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9613682305665</v>
+        <v>363.9513706088191</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35015,28 +35199,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3289403062594484</v>
+        <v>0.3376732473421055</v>
       </c>
       <c r="J8" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K8" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2027642099476504</v>
+        <v>0.2112868148593027</v>
       </c>
       <c r="M8" t="n">
-        <v>3.691114364609127</v>
+        <v>3.711344334426586</v>
       </c>
       <c r="N8" t="n">
-        <v>22.74706666309479</v>
+        <v>22.93439871624423</v>
       </c>
       <c r="O8" t="n">
-        <v>4.769388499912204</v>
+        <v>4.788987232833705</v>
       </c>
       <c r="P8" t="n">
-        <v>356.0384706665126</v>
+        <v>355.9454020850052</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35093,28 +35277,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5482865613317549</v>
+        <v>0.5571921244884521</v>
       </c>
       <c r="J9" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="K9" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4474467010024042</v>
+        <v>0.4546625717120187</v>
       </c>
       <c r="M9" t="n">
-        <v>3.491940018691825</v>
+        <v>3.51342552774881</v>
       </c>
       <c r="N9" t="n">
-        <v>19.84923605815076</v>
+        <v>20.06473300777426</v>
       </c>
       <c r="O9" t="n">
-        <v>4.455248147763575</v>
+        <v>4.479367478536926</v>
       </c>
       <c r="P9" t="n">
-        <v>347.830610581047</v>
+        <v>347.7357016394939</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35152,7 +35336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J735"/>
+  <dimension ref="A1:J739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73371,6 +73555,214 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-39.84115622351555,176.9984018296148</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-39.84159875392927,176.99771085742304</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-39.842070140643,176.99705955976663</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-39.84257206172336,176.99652245198212</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-39.84312370215674,176.99606008290226</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-39.84372350913715,176.99567387199892</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-39.84434728249154,176.99537415439755</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-39.845007108285834,176.99512474217724</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-39.841140585914964,176.99838251343806</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-39.84158474517432,176.99769355331634</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-39.842064682538116,176.9970526108781</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-39.84256683391834,176.99651295295232</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-39.84312117924022,176.9960534983356</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-39.84371961402251,176.99566055921886</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-39.84434672125625,176.99537120835777</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-39.84500740389091,176.9951264504534</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-39.841133548993504,176.9983738211614</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-39.84158181310897,176.99768993152745</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-39.842066865780126,176.9970553904334</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-39.84256955237706,176.99651789244763</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-39.84312194011985,176.99605548415724</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-39.84371980558556,176.9956612139457</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-39.844346872358074,176.99537200152233</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-39.84500697033678,176.99512394498169</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-39.84111667341029,176.99835297580154</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-39.84157138798661,176.99767705405839</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-39.842058453876646,176.99704468097136</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-39.84256458596194,176.99650886836992</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-39.843120578545765,176.99605193058173</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-39.84372149772569,176.9956669973664</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-39.84434790848466,176.99537744036502</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-39.84500823158503,176.9951312336268</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J739"/>
+  <dimension ref="A1:J743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27046,6 +27046,150 @@
       <c r="J739" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="C740" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="D740" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="E740" t="n">
+        <v>378.22</v>
+      </c>
+      <c r="F740" t="n">
+        <v>372.85</v>
+      </c>
+      <c r="G740" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="H740" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="I740" t="n">
+        <v>370.39</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>349.93</v>
+      </c>
+      <c r="C741" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="D741" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="E741" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="F741" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="G741" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="H741" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="I741" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="C742" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="D742" t="n">
+        <v>366.49</v>
+      </c>
+      <c r="E742" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="F742" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="G742" t="n">
+        <v>376.73</v>
+      </c>
+      <c r="H742" t="n">
+        <v>372.58</v>
+      </c>
+      <c r="I742" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="C743" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="D743" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="E743" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="F743" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="G743" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="H743" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="I743" t="n">
+        <v>371</v>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B750"/>
+  <dimension ref="A1:B754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34563,6 +34707,46 @@
       </c>
       <c r="B750" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-26 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -34731,28 +34915,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2717462045574097</v>
+        <v>0.2802732379924048</v>
       </c>
       <c r="J2" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K2" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003173665167479078</v>
+        <v>0.003415405560103446</v>
       </c>
       <c r="M2" t="n">
-        <v>31.00538869066966</v>
+        <v>30.90797373987396</v>
       </c>
       <c r="N2" t="n">
-        <v>1249.777542851336</v>
+        <v>1244.460972768022</v>
       </c>
       <c r="O2" t="n">
-        <v>35.35219290017715</v>
+        <v>35.27691841371667</v>
       </c>
       <c r="P2" t="n">
-        <v>328.5937846889111</v>
+        <v>328.5027858621497</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34809,28 +34993,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8786940379325925</v>
+        <v>0.8810230231722864</v>
       </c>
       <c r="J3" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K3" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4724360379790395</v>
+        <v>0.4768642889760455</v>
       </c>
       <c r="M3" t="n">
-        <v>5.530869032661677</v>
+        <v>5.513292279811623</v>
       </c>
       <c r="N3" t="n">
-        <v>46.45738992645208</v>
+        <v>46.23173726873362</v>
       </c>
       <c r="O3" t="n">
-        <v>6.815965810246709</v>
+        <v>6.799392419086695</v>
       </c>
       <c r="P3" t="n">
-        <v>336.626970145074</v>
+        <v>336.6020875250856</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34887,28 +35071,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.010975196373253</v>
+        <v>1.009600033670012</v>
       </c>
       <c r="J4" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K4" t="n">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6234119832283921</v>
+        <v>0.6257631031135645</v>
       </c>
       <c r="M4" t="n">
-        <v>4.536209618015935</v>
+        <v>4.517445033578371</v>
       </c>
       <c r="N4" t="n">
-        <v>33.11371645875008</v>
+        <v>32.94424808569447</v>
       </c>
       <c r="O4" t="n">
-        <v>5.754451881695604</v>
+        <v>5.73970801397549</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9023669366072</v>
+        <v>340.9171137811949</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34965,28 +35149,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.083972436473473</v>
+        <v>1.079247599005792</v>
       </c>
       <c r="J5" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K5" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6811467364951451</v>
+        <v>0.6813907676721154</v>
       </c>
       <c r="M5" t="n">
-        <v>4.359044099152356</v>
+        <v>4.354980659628102</v>
       </c>
       <c r="N5" t="n">
-        <v>29.63698422676292</v>
+        <v>29.56993873531879</v>
       </c>
       <c r="O5" t="n">
-        <v>5.443986060485728</v>
+        <v>5.437824816534529</v>
       </c>
       <c r="P5" t="n">
-        <v>353.1467768841694</v>
+        <v>353.1972685264525</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35043,28 +35227,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8438471017360613</v>
+        <v>0.8395877193717232</v>
       </c>
       <c r="J6" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K6" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5846152933036199</v>
+        <v>0.5846372873091719</v>
       </c>
       <c r="M6" t="n">
-        <v>4.132338643486166</v>
+        <v>4.129448789294147</v>
       </c>
       <c r="N6" t="n">
-        <v>27.26184233936884</v>
+        <v>27.1906307881008</v>
       </c>
       <c r="O6" t="n">
-        <v>5.221287421639307</v>
+        <v>5.214463614610884</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2683973594289</v>
+        <v>354.3139123050634</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35121,28 +35305,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.419917969661494</v>
+        <v>0.4215265564228082</v>
       </c>
       <c r="J7" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K7" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2733247887720994</v>
+        <v>0.2773558986267</v>
       </c>
       <c r="M7" t="n">
-        <v>3.847398849827586</v>
+        <v>3.833479956141614</v>
       </c>
       <c r="N7" t="n">
-        <v>25.2602467760445</v>
+        <v>25.13524182284901</v>
       </c>
       <c r="O7" t="n">
-        <v>5.025957299464898</v>
+        <v>5.013505941240023</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9513706088191</v>
+        <v>363.9341786142181</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35199,28 +35383,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3376732473421055</v>
+        <v>0.3461278074085686</v>
       </c>
       <c r="J8" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K8" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2112868148593027</v>
+        <v>0.2196545596242397</v>
       </c>
       <c r="M8" t="n">
-        <v>3.711344334426586</v>
+        <v>3.731070335446856</v>
       </c>
       <c r="N8" t="n">
-        <v>22.93439871624423</v>
+        <v>23.10818245674959</v>
       </c>
       <c r="O8" t="n">
-        <v>4.788987232833705</v>
+        <v>4.807097092502874</v>
       </c>
       <c r="P8" t="n">
-        <v>355.9454020850052</v>
+        <v>355.8550551889519</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35277,28 +35461,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5571921244884521</v>
+        <v>0.5663102967862139</v>
       </c>
       <c r="J9" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K9" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4546625717120187</v>
+        <v>0.4616922012840036</v>
       </c>
       <c r="M9" t="n">
-        <v>3.51342552774881</v>
+        <v>3.536744462234814</v>
       </c>
       <c r="N9" t="n">
-        <v>20.06473300777426</v>
+        <v>20.30173620740921</v>
       </c>
       <c r="O9" t="n">
-        <v>4.479367478536926</v>
+        <v>4.505744800519578</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7357016394939</v>
+        <v>347.6382601122133</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35336,7 +35520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J739"/>
+  <dimension ref="A1:J743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73763,6 +73947,214 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-39.84110429363607,176.9983376838452</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-39.841567152780186,176.9976718225877</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-39.84205460109603,176.99703977587515</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-39.84256416773745,176.99650810844764</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-39.843119216971544,176.9960483770063</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-39.84372156158003,176.9956672156087</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-39.84434706663182,176.9953730213053</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-39.84500762066798,176.9951277031893</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-39.8410199156397,176.99823345723743</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-39.841560832548566,176.99766401562496</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-39.84204862928565,176.9970321729771</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-39.84256228572728,176.9965046887975</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-39.84311933711046,176.99604869055707</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-39.843723764554454,176.99567474496814</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-39.844348383375916,176.99537993316795</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-39.84500840894803,176.99513225859252</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-39.84093312673124,176.99812625299438</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-39.8415582262673,176.99766079625928</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-39.84204702396017,176.99703012918752</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-39.842563069898205,176.99650611365172</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-39.84312069868465,176.9960522441325</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-39.84372344528284,176.9956736537566</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-39.844347412007366,176.99537483425289</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>-39.84500854689703,176.9951330557881</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-39.84085363528887,176.99802806316015</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-39.84155627155629,176.9976583817352</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-39.842046317616955,176.99702922992012</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-39.842563644956854,176.9965071585448</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-39.843122260490205,176.9960563202927</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-39.8437238922631,176.99567518145275</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-39.84434603050502,176.99536758246276</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>-39.845008822794995,176.99513465017927</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
